--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03A0170-B26B-4708-9439-1F5399E0DFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638FDF63-6731-4785-A0D0-68B0CBB7BB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -94,6 +94,12 @@
     <t>Q1</t>
   </si>
   <si>
+    <t>WZ08-2221(2/3) + WZ08-2222</t>
+  </si>
+  <si>
+    <t>IK Kunststoffverpackungen</t>
+  </si>
+  <si>
     <t>Q2</t>
   </si>
   <si>
@@ -101,12 +107,6 @@
   </si>
   <si>
     <t>Q4</t>
-  </si>
-  <si>
-    <t>WZ08-2221(2/3) + WZ08-2222</t>
-  </si>
-  <si>
-    <t>IK Kunststoffverpackungen</t>
   </si>
 </sst>
 </file>
@@ -124,10 +124,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,9 +185,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +225,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -262,7 +259,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -297,10 +293,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -476,11 +471,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="15" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -560,23 +550,11 @@
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2">
-        <v>151.27000000000001</v>
-      </c>
-      <c r="D2">
-        <v>102.05</v>
-      </c>
-      <c r="E2">
-        <v>129.43</v>
-      </c>
-      <c r="F2">
-        <v>231.91</v>
-      </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K2">
         <v>-4.5</v>
@@ -620,25 +598,13 @@
         <v>2015</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3">
-        <v>163.35</v>
-      </c>
-      <c r="D3">
-        <v>98.77</v>
-      </c>
-      <c r="E3">
-        <v>151.38</v>
-      </c>
-      <c r="F3">
-        <v>218.75</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K3">
         <v>-11.5</v>
@@ -682,25 +648,13 @@
         <v>2015</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>140.52000000000001</v>
-      </c>
-      <c r="D4">
-        <v>93.28</v>
-      </c>
-      <c r="E4">
-        <v>121.93</v>
-      </c>
-      <c r="F4">
-        <v>210.75</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K4">
         <v>-33.9</v>
@@ -744,25 +698,13 @@
         <v>2015</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5">
-        <v>126.18</v>
-      </c>
-      <c r="D5">
-        <v>86.02</v>
-      </c>
-      <c r="E5">
-        <v>107.37</v>
-      </c>
-      <c r="F5">
-        <v>194.98</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K5">
         <v>-4.9000000000000004</v>
@@ -808,23 +750,11 @@
       <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6">
-        <v>97.94</v>
-      </c>
-      <c r="D6">
-        <v>84.26</v>
-      </c>
-      <c r="E6">
-        <v>84.55</v>
-      </c>
-      <c r="F6">
-        <v>142.46</v>
-      </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K6">
         <v>2.8</v>
@@ -868,25 +798,13 @@
         <v>2016</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>114.73</v>
-      </c>
-      <c r="D7">
-        <v>85.33</v>
-      </c>
-      <c r="E7">
-        <v>109.98</v>
-      </c>
-      <c r="F7">
-        <v>137.84</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K7">
         <v>-6.9</v>
@@ -930,25 +848,13 @@
         <v>2016</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>118.28</v>
-      </c>
-      <c r="D8">
-        <v>106.33</v>
-      </c>
-      <c r="E8">
-        <v>111.06</v>
-      </c>
-      <c r="F8">
-        <v>143.66</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K8">
         <v>-14.5</v>
@@ -992,25 +898,13 @@
         <v>2016</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9">
-        <v>143.88999999999999</v>
-      </c>
-      <c r="D9">
-        <v>151.26</v>
-      </c>
-      <c r="E9">
-        <v>125.3</v>
-      </c>
-      <c r="F9">
-        <v>197.89</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K9">
         <v>-8</v>
@@ -1056,23 +950,11 @@
       <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="C10">
-        <v>152.76</v>
-      </c>
-      <c r="D10">
-        <v>140.56</v>
-      </c>
-      <c r="E10">
-        <v>135.41</v>
-      </c>
-      <c r="F10">
-        <v>208.83</v>
-      </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1116,25 +998,13 @@
         <v>2017</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>131.16999999999999</v>
-      </c>
-      <c r="D11">
-        <v>129.41999999999999</v>
-      </c>
-      <c r="E11">
-        <v>122.16</v>
-      </c>
-      <c r="F11">
-        <v>158.94</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K11">
         <v>-23.5</v>
@@ -1178,25 +1048,13 @@
         <v>2017</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12">
-        <v>129.72</v>
-      </c>
-      <c r="D12">
-        <v>139.25</v>
-      </c>
-      <c r="E12">
-        <v>117.19</v>
-      </c>
-      <c r="F12">
-        <v>164.77</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1240,25 +1098,13 @@
         <v>2017</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13">
-        <v>157.34</v>
-      </c>
-      <c r="D13">
-        <v>147.18</v>
-      </c>
-      <c r="E13">
-        <v>137.88</v>
-      </c>
-      <c r="F13">
-        <v>219.17</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K13">
         <v>-12</v>
@@ -1304,23 +1150,11 @@
       <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="C14">
-        <v>159.55000000000001</v>
-      </c>
-      <c r="D14">
-        <v>145.74</v>
-      </c>
-      <c r="E14">
-        <v>144.53</v>
-      </c>
-      <c r="F14">
-        <v>209.05</v>
-      </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K14">
         <v>-5</v>
@@ -1364,25 +1198,13 @@
         <v>2018</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15">
-        <v>178.5</v>
-      </c>
-      <c r="D15">
-        <v>155.66999999999999</v>
-      </c>
-      <c r="E15">
-        <v>166.16</v>
-      </c>
-      <c r="F15">
-        <v>222.6</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K15">
         <v>9.8000000000000007</v>
@@ -1426,25 +1248,13 @@
         <v>2018</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16">
-        <v>192.67</v>
-      </c>
-      <c r="D16">
-        <v>171.44</v>
-      </c>
-      <c r="E16">
-        <v>172.13</v>
-      </c>
-      <c r="F16">
-        <v>261.07</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K16">
         <v>-20.3</v>
@@ -1488,25 +1298,13 @@
         <v>2018</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17">
-        <v>182.17</v>
-      </c>
-      <c r="D17">
-        <v>160.81</v>
-      </c>
-      <c r="E17">
-        <v>157.91999999999999</v>
-      </c>
-      <c r="F17">
-        <v>261.83</v>
+        <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K17">
         <v>-21.7</v>
@@ -1552,23 +1350,11 @@
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18">
-        <v>159.05000000000001</v>
-      </c>
-      <c r="D18">
-        <v>145.72</v>
-      </c>
-      <c r="E18">
-        <v>148.01</v>
-      </c>
-      <c r="F18">
-        <v>196.36</v>
-      </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K18">
         <v>-13.1</v>
@@ -1612,25 +1398,13 @@
         <v>2019</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>152.87</v>
-      </c>
-      <c r="D19">
-        <v>119.73</v>
-      </c>
-      <c r="E19">
-        <v>160.94</v>
-      </c>
-      <c r="F19">
-        <v>138.36000000000001</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K19">
         <v>-20</v>
@@ -1674,25 +1448,13 @@
         <v>2019</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>135.49</v>
-      </c>
-      <c r="D20">
-        <v>107</v>
-      </c>
-      <c r="E20">
-        <v>147.26</v>
-      </c>
-      <c r="F20">
-        <v>108.4</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K20">
         <v>-17.399999999999999</v>
@@ -1736,25 +1498,13 @@
         <v>2019</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>143.38999999999999</v>
-      </c>
-      <c r="D21">
-        <v>114.7</v>
-      </c>
-      <c r="E21">
-        <v>148.97999999999999</v>
-      </c>
-      <c r="F21">
-        <v>135.02000000000001</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K21">
         <v>-39.299999999999997</v>
@@ -1800,23 +1550,11 @@
       <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22">
-        <v>117.53</v>
-      </c>
-      <c r="D22">
-        <v>120.22</v>
-      </c>
-      <c r="E22">
-        <v>122.11</v>
-      </c>
-      <c r="F22">
-        <v>102.9</v>
-      </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K22">
         <v>-25.2</v>
@@ -1860,25 +1598,13 @@
         <v>2020</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23">
-        <v>75.430000000000007</v>
-      </c>
-      <c r="D23">
-        <v>92.3</v>
-      </c>
-      <c r="E23">
-        <v>79.78</v>
-      </c>
-      <c r="F23">
-        <v>57.24</v>
+        <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J23">
         <v>-25.1</v>
@@ -1928,25 +1654,13 @@
         <v>2020</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24">
-        <v>93.46</v>
-      </c>
-      <c r="D24">
-        <v>83.24</v>
-      </c>
-      <c r="E24">
-        <v>97.9</v>
-      </c>
-      <c r="F24">
-        <v>83.07</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J24">
         <v>-32.700000000000003</v>
@@ -1996,25 +1710,13 @@
         <v>2020</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25">
-        <v>113.47</v>
-      </c>
-      <c r="D25">
-        <v>104.43</v>
-      </c>
-      <c r="E25">
-        <v>100.23</v>
-      </c>
-      <c r="F25">
-        <v>156.18</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J25">
         <v>-25</v>
@@ -2066,23 +1768,11 @@
       <c r="B26" t="s">
         <v>23</v>
       </c>
-      <c r="C26">
-        <v>148.51</v>
-      </c>
-      <c r="D26">
-        <v>133.16</v>
-      </c>
-      <c r="E26">
-        <v>134.08000000000001</v>
-      </c>
-      <c r="F26">
-        <v>196.7</v>
-      </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J26">
         <v>-4.9000000000000004</v>
@@ -2132,25 +1822,13 @@
         <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27">
-        <v>178.31</v>
-      </c>
-      <c r="D27">
-        <v>158.31</v>
-      </c>
-      <c r="E27">
-        <v>151.22</v>
-      </c>
-      <c r="F27">
-        <v>266.13</v>
+        <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2200,25 +1878,13 @@
         <v>2021</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28">
-        <v>250.39</v>
-      </c>
-      <c r="D28">
-        <v>235.79</v>
-      </c>
-      <c r="E28">
-        <v>163.98</v>
-      </c>
-      <c r="F28">
-        <v>515.91999999999996</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H28" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J28">
         <v>17.3</v>
@@ -2268,25 +1934,13 @@
         <v>2021</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29">
-        <v>382.6</v>
-      </c>
-      <c r="D29">
-        <v>275.74</v>
-      </c>
-      <c r="E29">
-        <v>183.82</v>
-      </c>
-      <c r="F29">
-        <v>1015.22</v>
+        <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H29" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J29">
         <v>6.8</v>
@@ -2338,23 +1992,11 @@
       <c r="B30" t="s">
         <v>23</v>
       </c>
-      <c r="C30">
-        <v>437.37</v>
-      </c>
-      <c r="D30">
-        <v>411.54</v>
-      </c>
-      <c r="E30">
-        <v>230.82</v>
-      </c>
-      <c r="F30">
-        <v>1069.3900000000001</v>
-      </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H30" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J30">
         <v>0.8</v>
@@ -2404,25 +2046,13 @@
         <v>2022</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31">
-        <v>477.47</v>
-      </c>
-      <c r="D31">
-        <v>579.74</v>
-      </c>
-      <c r="E31">
-        <v>277.58999999999997</v>
-      </c>
-      <c r="F31">
-        <v>1051.21</v>
+        <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J31">
         <v>-6.7</v>
@@ -2472,25 +2102,13 @@
         <v>2022</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32">
-        <v>718.47</v>
-      </c>
-      <c r="D32">
-        <v>672.34</v>
-      </c>
-      <c r="E32">
-        <v>255.98</v>
-      </c>
-      <c r="F32">
-        <v>2130.06</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H32" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J32">
         <v>-0.9</v>
@@ -2540,25 +2158,13 @@
         <v>2022</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33">
-        <v>432.37</v>
-      </c>
-      <c r="D33">
-        <v>544.53</v>
-      </c>
-      <c r="E33">
-        <v>229.63</v>
-      </c>
-      <c r="F33">
-        <v>1011.78</v>
+        <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J33">
         <v>-27.7</v>
@@ -2610,23 +2216,11 @@
       <c r="B34" t="s">
         <v>23</v>
       </c>
-      <c r="C34">
-        <v>296.26</v>
-      </c>
-      <c r="D34">
-        <v>344.52</v>
-      </c>
-      <c r="E34">
-        <v>202.16</v>
-      </c>
-      <c r="F34">
-        <v>566.32000000000005</v>
-      </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J34">
         <v>-16.2</v>
@@ -2676,25 +2270,13 @@
         <v>2023</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35">
-        <v>234.31</v>
-      </c>
-      <c r="D35">
-        <v>231.49</v>
-      </c>
-      <c r="E35">
-        <v>188.68</v>
-      </c>
-      <c r="F35">
-        <v>373.05</v>
+        <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H35" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J35">
         <v>-23.5</v>
@@ -2744,25 +2326,25 @@
         <v>2023</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C36">
-        <v>241.89</v>
+        <v>266.47000000000003</v>
       </c>
       <c r="D36">
-        <v>215.1</v>
+        <v>237.47</v>
       </c>
       <c r="E36">
-        <v>208.61</v>
+        <v>229.02</v>
       </c>
       <c r="F36">
-        <v>350.45</v>
+        <v>388.29</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J36">
         <v>-32.6</v>
@@ -2812,25 +2394,25 @@
         <v>2023</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C37">
-        <v>256.58999999999997</v>
+        <v>256.51</v>
       </c>
       <c r="D37">
-        <v>212.81</v>
+        <v>212.78</v>
       </c>
       <c r="E37">
-        <v>203.33</v>
+        <v>203.23</v>
       </c>
       <c r="F37">
         <v>430.58</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J37">
         <v>-32.6</v>
@@ -2886,19 +2468,19 @@
         <v>219.51</v>
       </c>
       <c r="D38">
-        <v>188.21</v>
+        <v>187.93</v>
       </c>
       <c r="E38">
-        <v>198.78</v>
+        <v>198.8</v>
       </c>
       <c r="F38">
         <v>291.47000000000003</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J38">
         <v>-28</v>
@@ -2948,25 +2530,25 @@
         <v>2024</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39">
-        <v>237.77</v>
+        <v>237.79</v>
       </c>
       <c r="D39">
-        <v>206.2</v>
+        <v>206.43</v>
       </c>
       <c r="E39">
-        <v>208.5</v>
+        <v>208.49</v>
       </c>
       <c r="F39">
         <v>335.66</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J39">
         <v>-18.3</v>
@@ -3016,25 +2598,25 @@
         <v>2024</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C40">
-        <v>233.47</v>
+        <v>233.39</v>
       </c>
       <c r="D40">
-        <v>207.69</v>
+        <v>207.24</v>
       </c>
       <c r="E40">
-        <v>189.3</v>
+        <v>189.23</v>
       </c>
       <c r="F40">
         <v>374.65</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J40">
         <v>-13.7</v>
@@ -3084,25 +2666,25 @@
         <v>2024</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C41">
-        <v>248.57</v>
+        <v>248.71</v>
       </c>
       <c r="D41">
-        <v>213.06</v>
+        <v>213.7</v>
       </c>
       <c r="E41">
-        <v>183.01</v>
+        <v>183.15</v>
       </c>
       <c r="F41">
         <v>457.27</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J41">
         <v>-20.2</v>
@@ -3155,22 +2737,22 @@
         <v>23</v>
       </c>
       <c r="C42">
-        <v>258.89999999999998</v>
+        <v>259.07</v>
       </c>
       <c r="D42">
-        <v>176.1</v>
+        <v>176.66</v>
       </c>
       <c r="E42">
-        <v>188.3</v>
+        <v>188.48</v>
       </c>
       <c r="F42">
         <v>496.95</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J42">
         <v>-17.39130434782609</v>
@@ -3220,25 +2802,25 @@
         <v>2025</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C43">
-        <v>206.44</v>
+        <v>206.46</v>
       </c>
       <c r="D43">
-        <v>152.43</v>
+        <v>152.63999999999999</v>
       </c>
       <c r="E43">
-        <v>155.36000000000001</v>
+        <v>155.37</v>
       </c>
       <c r="F43">
         <v>376.9</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J43">
         <v>-15.2</v>
@@ -3288,25 +2870,25 @@
         <v>2025</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C44">
-        <v>198.5</v>
+        <v>198.46</v>
       </c>
       <c r="D44">
-        <v>156.02000000000001</v>
+        <v>155.97</v>
       </c>
       <c r="E44">
-        <v>154.06</v>
+        <v>154.01</v>
       </c>
       <c r="F44">
         <v>345.47</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I44">
         <v>-3.33</v>
@@ -3359,25 +2941,25 @@
         <v>2025</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C45">
-        <v>184.44</v>
+        <v>184.42</v>
       </c>
       <c r="D45">
-        <v>151.35</v>
+        <v>151.30000000000001</v>
       </c>
       <c r="E45">
-        <v>143.11000000000001</v>
+        <v>143.09</v>
       </c>
       <c r="F45">
         <v>319.2</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H45" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I45">
         <v>-27.9</v>
@@ -3433,22 +3015,22 @@
         <v>23</v>
       </c>
       <c r="C46">
-        <v>233.5</v>
+        <v>234.29</v>
       </c>
       <c r="D46">
-        <v>170.25</v>
+        <v>170.29</v>
       </c>
       <c r="E46">
-        <v>176.51</v>
+        <v>177</v>
       </c>
       <c r="F46">
-        <v>424.56</v>
+        <v>426.49</v>
       </c>
       <c r="G46" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I46">
         <v>-1.830000000000001</v>
@@ -3501,13 +3083,25 @@
         <v>2026</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="C47">
+        <v>279.62</v>
+      </c>
+      <c r="D47">
+        <v>196.23</v>
+      </c>
+      <c r="E47">
+        <v>219.75</v>
+      </c>
+      <c r="F47">
+        <v>485.39</v>
       </c>
       <c r="G47" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H47" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I47">
         <v>-3.8100000000000018</v>
@@ -3526,6 +3120,33 @@
       </c>
       <c r="N47">
         <v>-51.43</v>
+      </c>
+      <c r="O47">
+        <v>506.33333333333331</v>
+      </c>
+      <c r="P47">
+        <v>89351.666666666672</v>
+      </c>
+      <c r="Q47">
+        <v>33785000</v>
+      </c>
+      <c r="R47">
+        <v>1194821334</v>
+      </c>
+      <c r="S47">
+        <v>6912040000</v>
+      </c>
+      <c r="T47">
+        <v>3652099333</v>
+      </c>
+      <c r="U47">
+        <v>3259940667</v>
+      </c>
+      <c r="V47">
+        <v>1964740000</v>
+      </c>
+      <c r="W47">
+        <v>1295201667</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -3533,13 +3154,13 @@
         <v>2026</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I48">
         <v>-19.559999999999999</v>
@@ -3565,16 +3186,16 @@
         <v>2026</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H49" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638FDF63-6731-4785-A0D0-68B0CBB7BB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748A13A3-E2DD-4349-B01C-2089D0DCE072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,6 +471,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -550,6 +554,18 @@
       <c r="B2" t="s">
         <v>23</v>
       </c>
+      <c r="C2">
+        <v>151.27000000000001</v>
+      </c>
+      <c r="D2">
+        <v>102.05</v>
+      </c>
+      <c r="E2">
+        <v>129.43</v>
+      </c>
+      <c r="F2">
+        <v>231.91</v>
+      </c>
       <c r="G2" t="s">
         <v>24</v>
       </c>
@@ -600,6 +616,18 @@
       <c r="B3" t="s">
         <v>26</v>
       </c>
+      <c r="C3">
+        <v>163.35</v>
+      </c>
+      <c r="D3">
+        <v>98.77</v>
+      </c>
+      <c r="E3">
+        <v>151.38</v>
+      </c>
+      <c r="F3">
+        <v>218.75</v>
+      </c>
       <c r="G3" t="s">
         <v>24</v>
       </c>
@@ -650,6 +678,18 @@
       <c r="B4" t="s">
         <v>27</v>
       </c>
+      <c r="C4">
+        <v>140.52000000000001</v>
+      </c>
+      <c r="D4">
+        <v>93.28</v>
+      </c>
+      <c r="E4">
+        <v>121.93</v>
+      </c>
+      <c r="F4">
+        <v>210.75</v>
+      </c>
       <c r="G4" t="s">
         <v>24</v>
       </c>
@@ -700,6 +740,18 @@
       <c r="B5" t="s">
         <v>28</v>
       </c>
+      <c r="C5">
+        <v>126.18</v>
+      </c>
+      <c r="D5">
+        <v>86.02</v>
+      </c>
+      <c r="E5">
+        <v>107.37</v>
+      </c>
+      <c r="F5">
+        <v>194.98</v>
+      </c>
       <c r="G5" t="s">
         <v>24</v>
       </c>
@@ -750,6 +802,18 @@
       <c r="B6" t="s">
         <v>23</v>
       </c>
+      <c r="C6">
+        <v>97.94</v>
+      </c>
+      <c r="D6">
+        <v>84.26</v>
+      </c>
+      <c r="E6">
+        <v>84.55</v>
+      </c>
+      <c r="F6">
+        <v>142.46</v>
+      </c>
       <c r="G6" t="s">
         <v>24</v>
       </c>
@@ -800,6 +864,18 @@
       <c r="B7" t="s">
         <v>26</v>
       </c>
+      <c r="C7">
+        <v>114.73</v>
+      </c>
+      <c r="D7">
+        <v>85.33</v>
+      </c>
+      <c r="E7">
+        <v>109.98</v>
+      </c>
+      <c r="F7">
+        <v>137.84</v>
+      </c>
       <c r="G7" t="s">
         <v>24</v>
       </c>
@@ -850,6 +926,18 @@
       <c r="B8" t="s">
         <v>27</v>
       </c>
+      <c r="C8">
+        <v>118.28</v>
+      </c>
+      <c r="D8">
+        <v>106.33</v>
+      </c>
+      <c r="E8">
+        <v>111.06</v>
+      </c>
+      <c r="F8">
+        <v>143.66</v>
+      </c>
       <c r="G8" t="s">
         <v>24</v>
       </c>
@@ -900,6 +988,18 @@
       <c r="B9" t="s">
         <v>28</v>
       </c>
+      <c r="C9">
+        <v>143.88999999999999</v>
+      </c>
+      <c r="D9">
+        <v>151.26</v>
+      </c>
+      <c r="E9">
+        <v>125.3</v>
+      </c>
+      <c r="F9">
+        <v>197.89</v>
+      </c>
       <c r="G9" t="s">
         <v>24</v>
       </c>
@@ -950,6 +1050,18 @@
       <c r="B10" t="s">
         <v>23</v>
       </c>
+      <c r="C10">
+        <v>152.76</v>
+      </c>
+      <c r="D10">
+        <v>140.56</v>
+      </c>
+      <c r="E10">
+        <v>135.41</v>
+      </c>
+      <c r="F10">
+        <v>208.83</v>
+      </c>
       <c r="G10" t="s">
         <v>24</v>
       </c>
@@ -1000,6 +1112,18 @@
       <c r="B11" t="s">
         <v>26</v>
       </c>
+      <c r="C11">
+        <v>131.16999999999999</v>
+      </c>
+      <c r="D11">
+        <v>129.41999999999999</v>
+      </c>
+      <c r="E11">
+        <v>122.16</v>
+      </c>
+      <c r="F11">
+        <v>158.94</v>
+      </c>
       <c r="G11" t="s">
         <v>24</v>
       </c>
@@ -1050,6 +1174,18 @@
       <c r="B12" t="s">
         <v>27</v>
       </c>
+      <c r="C12">
+        <v>129.72</v>
+      </c>
+      <c r="D12">
+        <v>139.25</v>
+      </c>
+      <c r="E12">
+        <v>117.19</v>
+      </c>
+      <c r="F12">
+        <v>164.77</v>
+      </c>
       <c r="G12" t="s">
         <v>24</v>
       </c>
@@ -1100,6 +1236,18 @@
       <c r="B13" t="s">
         <v>28</v>
       </c>
+      <c r="C13">
+        <v>157.34</v>
+      </c>
+      <c r="D13">
+        <v>147.18</v>
+      </c>
+      <c r="E13">
+        <v>137.88</v>
+      </c>
+      <c r="F13">
+        <v>219.17</v>
+      </c>
       <c r="G13" t="s">
         <v>24</v>
       </c>
@@ -1150,6 +1298,18 @@
       <c r="B14" t="s">
         <v>23</v>
       </c>
+      <c r="C14">
+        <v>159.55000000000001</v>
+      </c>
+      <c r="D14">
+        <v>145.74</v>
+      </c>
+      <c r="E14">
+        <v>144.53</v>
+      </c>
+      <c r="F14">
+        <v>209.05</v>
+      </c>
       <c r="G14" t="s">
         <v>24</v>
       </c>
@@ -1200,6 +1360,18 @@
       <c r="B15" t="s">
         <v>26</v>
       </c>
+      <c r="C15">
+        <v>178.5</v>
+      </c>
+      <c r="D15">
+        <v>155.66999999999999</v>
+      </c>
+      <c r="E15">
+        <v>166.16</v>
+      </c>
+      <c r="F15">
+        <v>222.6</v>
+      </c>
       <c r="G15" t="s">
         <v>24</v>
       </c>
@@ -1250,6 +1422,18 @@
       <c r="B16" t="s">
         <v>27</v>
       </c>
+      <c r="C16">
+        <v>192.67</v>
+      </c>
+      <c r="D16">
+        <v>171.44</v>
+      </c>
+      <c r="E16">
+        <v>172.13</v>
+      </c>
+      <c r="F16">
+        <v>261.07</v>
+      </c>
       <c r="G16" t="s">
         <v>24</v>
       </c>
@@ -1300,6 +1484,18 @@
       <c r="B17" t="s">
         <v>28</v>
       </c>
+      <c r="C17">
+        <v>182.17</v>
+      </c>
+      <c r="D17">
+        <v>160.81</v>
+      </c>
+      <c r="E17">
+        <v>157.91999999999999</v>
+      </c>
+      <c r="F17">
+        <v>261.83</v>
+      </c>
       <c r="G17" t="s">
         <v>24</v>
       </c>
@@ -1350,6 +1546,18 @@
       <c r="B18" t="s">
         <v>23</v>
       </c>
+      <c r="C18">
+        <v>159.05000000000001</v>
+      </c>
+      <c r="D18">
+        <v>145.72</v>
+      </c>
+      <c r="E18">
+        <v>148.01</v>
+      </c>
+      <c r="F18">
+        <v>196.36</v>
+      </c>
       <c r="G18" t="s">
         <v>24</v>
       </c>
@@ -1400,6 +1608,18 @@
       <c r="B19" t="s">
         <v>26</v>
       </c>
+      <c r="C19">
+        <v>152.87</v>
+      </c>
+      <c r="D19">
+        <v>119.73</v>
+      </c>
+      <c r="E19">
+        <v>160.94</v>
+      </c>
+      <c r="F19">
+        <v>138.36000000000001</v>
+      </c>
       <c r="G19" t="s">
         <v>24</v>
       </c>
@@ -1450,6 +1670,18 @@
       <c r="B20" t="s">
         <v>27</v>
       </c>
+      <c r="C20">
+        <v>135.49</v>
+      </c>
+      <c r="D20">
+        <v>107</v>
+      </c>
+      <c r="E20">
+        <v>147.26</v>
+      </c>
+      <c r="F20">
+        <v>108.4</v>
+      </c>
       <c r="G20" t="s">
         <v>24</v>
       </c>
@@ -1500,6 +1732,18 @@
       <c r="B21" t="s">
         <v>28</v>
       </c>
+      <c r="C21">
+        <v>143.38999999999999</v>
+      </c>
+      <c r="D21">
+        <v>114.7</v>
+      </c>
+      <c r="E21">
+        <v>148.97999999999999</v>
+      </c>
+      <c r="F21">
+        <v>135.02000000000001</v>
+      </c>
       <c r="G21" t="s">
         <v>24</v>
       </c>
@@ -1550,6 +1794,18 @@
       <c r="B22" t="s">
         <v>23</v>
       </c>
+      <c r="C22">
+        <v>117.53</v>
+      </c>
+      <c r="D22">
+        <v>120.22</v>
+      </c>
+      <c r="E22">
+        <v>122.11</v>
+      </c>
+      <c r="F22">
+        <v>102.9</v>
+      </c>
       <c r="G22" t="s">
         <v>24</v>
       </c>
@@ -1600,6 +1856,18 @@
       <c r="B23" t="s">
         <v>26</v>
       </c>
+      <c r="C23">
+        <v>75.430000000000007</v>
+      </c>
+      <c r="D23">
+        <v>92.3</v>
+      </c>
+      <c r="E23">
+        <v>79.78</v>
+      </c>
+      <c r="F23">
+        <v>57.24</v>
+      </c>
       <c r="G23" t="s">
         <v>24</v>
       </c>
@@ -1656,6 +1924,18 @@
       <c r="B24" t="s">
         <v>27</v>
       </c>
+      <c r="C24">
+        <v>93.46</v>
+      </c>
+      <c r="D24">
+        <v>83.24</v>
+      </c>
+      <c r="E24">
+        <v>97.9</v>
+      </c>
+      <c r="F24">
+        <v>83.07</v>
+      </c>
       <c r="G24" t="s">
         <v>24</v>
       </c>
@@ -1712,6 +1992,18 @@
       <c r="B25" t="s">
         <v>28</v>
       </c>
+      <c r="C25">
+        <v>113.47</v>
+      </c>
+      <c r="D25">
+        <v>104.43</v>
+      </c>
+      <c r="E25">
+        <v>100.23</v>
+      </c>
+      <c r="F25">
+        <v>156.18</v>
+      </c>
       <c r="G25" t="s">
         <v>24</v>
       </c>
@@ -1768,6 +2060,18 @@
       <c r="B26" t="s">
         <v>23</v>
       </c>
+      <c r="C26">
+        <v>148.51</v>
+      </c>
+      <c r="D26">
+        <v>133.16</v>
+      </c>
+      <c r="E26">
+        <v>134.08000000000001</v>
+      </c>
+      <c r="F26">
+        <v>196.7</v>
+      </c>
       <c r="G26" t="s">
         <v>24</v>
       </c>
@@ -1824,6 +2128,18 @@
       <c r="B27" t="s">
         <v>26</v>
       </c>
+      <c r="C27">
+        <v>178.31</v>
+      </c>
+      <c r="D27">
+        <v>158.31</v>
+      </c>
+      <c r="E27">
+        <v>151.22</v>
+      </c>
+      <c r="F27">
+        <v>266.13</v>
+      </c>
       <c r="G27" t="s">
         <v>24</v>
       </c>
@@ -1880,6 +2196,18 @@
       <c r="B28" t="s">
         <v>27</v>
       </c>
+      <c r="C28">
+        <v>250.39</v>
+      </c>
+      <c r="D28">
+        <v>235.79</v>
+      </c>
+      <c r="E28">
+        <v>163.98</v>
+      </c>
+      <c r="F28">
+        <v>515.91999999999996</v>
+      </c>
       <c r="G28" t="s">
         <v>24</v>
       </c>
@@ -1936,6 +2264,18 @@
       <c r="B29" t="s">
         <v>28</v>
       </c>
+      <c r="C29">
+        <v>382.6</v>
+      </c>
+      <c r="D29">
+        <v>275.74</v>
+      </c>
+      <c r="E29">
+        <v>183.82</v>
+      </c>
+      <c r="F29">
+        <v>1015.22</v>
+      </c>
       <c r="G29" t="s">
         <v>24</v>
       </c>
@@ -1992,6 +2332,18 @@
       <c r="B30" t="s">
         <v>23</v>
       </c>
+      <c r="C30">
+        <v>437.37</v>
+      </c>
+      <c r="D30">
+        <v>411.54</v>
+      </c>
+      <c r="E30">
+        <v>230.82</v>
+      </c>
+      <c r="F30">
+        <v>1069.3900000000001</v>
+      </c>
       <c r="G30" t="s">
         <v>24</v>
       </c>
@@ -2048,6 +2400,18 @@
       <c r="B31" t="s">
         <v>26</v>
       </c>
+      <c r="C31">
+        <v>477.47</v>
+      </c>
+      <c r="D31">
+        <v>579.74</v>
+      </c>
+      <c r="E31">
+        <v>277.58999999999997</v>
+      </c>
+      <c r="F31">
+        <v>1051.21</v>
+      </c>
       <c r="G31" t="s">
         <v>24</v>
       </c>
@@ -2104,6 +2468,18 @@
       <c r="B32" t="s">
         <v>27</v>
       </c>
+      <c r="C32">
+        <v>718.47</v>
+      </c>
+      <c r="D32">
+        <v>672.34</v>
+      </c>
+      <c r="E32">
+        <v>255.98</v>
+      </c>
+      <c r="F32">
+        <v>2130.06</v>
+      </c>
       <c r="G32" t="s">
         <v>24</v>
       </c>
@@ -2160,6 +2536,18 @@
       <c r="B33" t="s">
         <v>28</v>
       </c>
+      <c r="C33">
+        <v>432.37</v>
+      </c>
+      <c r="D33">
+        <v>544.53</v>
+      </c>
+      <c r="E33">
+        <v>229.63</v>
+      </c>
+      <c r="F33">
+        <v>1011.78</v>
+      </c>
       <c r="G33" t="s">
         <v>24</v>
       </c>
@@ -2216,6 +2604,18 @@
       <c r="B34" t="s">
         <v>23</v>
       </c>
+      <c r="C34">
+        <v>296.26</v>
+      </c>
+      <c r="D34">
+        <v>344.52</v>
+      </c>
+      <c r="E34">
+        <v>202.16</v>
+      </c>
+      <c r="F34">
+        <v>566.32000000000005</v>
+      </c>
       <c r="G34" t="s">
         <v>24</v>
       </c>
@@ -2272,6 +2672,18 @@
       <c r="B35" t="s">
         <v>26</v>
       </c>
+      <c r="C35">
+        <v>234.31</v>
+      </c>
+      <c r="D35">
+        <v>231.49</v>
+      </c>
+      <c r="E35">
+        <v>188.68</v>
+      </c>
+      <c r="F35">
+        <v>373.05</v>
+      </c>
       <c r="G35" t="s">
         <v>24</v>
       </c>
@@ -2329,16 +2741,16 @@
         <v>27</v>
       </c>
       <c r="C36">
-        <v>266.47000000000003</v>
+        <v>241.89</v>
       </c>
       <c r="D36">
-        <v>237.47</v>
+        <v>215.1</v>
       </c>
       <c r="E36">
-        <v>229.02</v>
+        <v>208.61</v>
       </c>
       <c r="F36">
-        <v>388.29</v>
+        <v>350.45</v>
       </c>
       <c r="G36" t="s">
         <v>24</v>
@@ -2397,13 +2809,13 @@
         <v>28</v>
       </c>
       <c r="C37">
-        <v>256.51</v>
+        <v>256.58999999999997</v>
       </c>
       <c r="D37">
-        <v>212.78</v>
+        <v>212.82</v>
       </c>
       <c r="E37">
-        <v>203.23</v>
+        <v>203.33</v>
       </c>
       <c r="F37">
         <v>430.58</v>
@@ -2468,10 +2880,10 @@
         <v>219.51</v>
       </c>
       <c r="D38">
-        <v>187.93</v>
+        <v>188.21</v>
       </c>
       <c r="E38">
-        <v>198.8</v>
+        <v>198.78</v>
       </c>
       <c r="F38">
         <v>291.47000000000003</v>
@@ -2533,13 +2945,13 @@
         <v>26</v>
       </c>
       <c r="C39">
-        <v>237.79</v>
+        <v>237.77</v>
       </c>
       <c r="D39">
-        <v>206.43</v>
+        <v>206.2</v>
       </c>
       <c r="E39">
-        <v>208.49</v>
+        <v>208.5</v>
       </c>
       <c r="F39">
         <v>335.66</v>
@@ -2601,13 +3013,13 @@
         <v>27</v>
       </c>
       <c r="C40">
-        <v>233.39</v>
+        <v>233.47</v>
       </c>
       <c r="D40">
-        <v>207.24</v>
+        <v>207.69</v>
       </c>
       <c r="E40">
-        <v>189.23</v>
+        <v>189.3</v>
       </c>
       <c r="F40">
         <v>374.65</v>
@@ -2669,13 +3081,13 @@
         <v>28</v>
       </c>
       <c r="C41">
-        <v>248.71</v>
+        <v>248.57</v>
       </c>
       <c r="D41">
-        <v>213.7</v>
+        <v>213.06</v>
       </c>
       <c r="E41">
-        <v>183.15</v>
+        <v>183.01</v>
       </c>
       <c r="F41">
         <v>457.27</v>
@@ -2737,13 +3149,13 @@
         <v>23</v>
       </c>
       <c r="C42">
-        <v>259.07</v>
+        <v>258.89999999999998</v>
       </c>
       <c r="D42">
-        <v>176.66</v>
+        <v>176.1</v>
       </c>
       <c r="E42">
-        <v>188.48</v>
+        <v>188.3</v>
       </c>
       <c r="F42">
         <v>496.95</v>
@@ -2805,13 +3217,13 @@
         <v>26</v>
       </c>
       <c r="C43">
-        <v>206.46</v>
+        <v>206.44</v>
       </c>
       <c r="D43">
-        <v>152.63999999999999</v>
+        <v>152.43</v>
       </c>
       <c r="E43">
-        <v>155.37</v>
+        <v>155.36000000000001</v>
       </c>
       <c r="F43">
         <v>376.9</v>
@@ -2873,13 +3285,13 @@
         <v>27</v>
       </c>
       <c r="C44">
-        <v>198.46</v>
+        <v>198.5</v>
       </c>
       <c r="D44">
-        <v>155.97</v>
+        <v>156.02000000000001</v>
       </c>
       <c r="E44">
-        <v>154.01</v>
+        <v>154.06</v>
       </c>
       <c r="F44">
         <v>345.47</v>
@@ -2944,13 +3356,13 @@
         <v>28</v>
       </c>
       <c r="C45">
-        <v>184.42</v>
+        <v>184.44</v>
       </c>
       <c r="D45">
-        <v>151.30000000000001</v>
+        <v>151.35</v>
       </c>
       <c r="E45">
-        <v>143.09</v>
+        <v>143.11000000000001</v>
       </c>
       <c r="F45">
         <v>319.2</v>
@@ -3015,16 +3427,16 @@
         <v>23</v>
       </c>
       <c r="C46">
-        <v>234.29</v>
+        <v>233.5</v>
       </c>
       <c r="D46">
-        <v>170.29</v>
+        <v>170.25</v>
       </c>
       <c r="E46">
-        <v>177</v>
+        <v>176.51</v>
       </c>
       <c r="F46">
-        <v>426.49</v>
+        <v>424.56</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
@@ -3086,13 +3498,13 @@
         <v>26</v>
       </c>
       <c r="C47">
-        <v>279.62</v>
+        <v>279.56</v>
       </c>
       <c r="D47">
-        <v>196.23</v>
+        <v>196.08</v>
       </c>
       <c r="E47">
-        <v>219.75</v>
+        <v>219.67</v>
       </c>
       <c r="F47">
         <v>485.39</v>

--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748A13A3-E2DD-4349-B01C-2089D0DCE072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765FBFEE-BDEB-44D4-9136-9347779E1EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -470,13 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -609,7 +605,7 @@
         <v>882786333</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2015</v>
       </c>
@@ -671,7 +667,7 @@
         <v>921369999</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -733,7 +729,7 @@
         <v>917048334</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2015</v>
       </c>
@@ -795,7 +791,7 @@
         <v>871193334</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2016</v>
       </c>
@@ -857,7 +853,7 @@
         <v>896210333</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -919,7 +915,7 @@
         <v>969759000</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -981,7 +977,7 @@
         <v>962288334</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2016</v>
       </c>
@@ -1043,7 +1039,7 @@
         <v>920080001</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2017</v>
       </c>
@@ -1105,7 +1101,7 @@
         <v>987298333</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2017</v>
       </c>
@@ -1167,7 +1163,7 @@
         <v>1041335000</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2017</v>
       </c>
@@ -1229,7 +1225,7 @@
         <v>1037990667</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2017</v>
       </c>
@@ -1291,7 +1287,7 @@
         <v>966161334</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2018</v>
       </c>
@@ -1353,7 +1349,7 @@
         <v>1046669667</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -1415,7 +1411,7 @@
         <v>1084889666</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2018</v>
       </c>
@@ -1477,7 +1473,7 @@
         <v>1051112334</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2018</v>
       </c>
@@ -1539,7 +1535,7 @@
         <v>987400666</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2019</v>
       </c>
@@ -1601,7 +1597,7 @@
         <v>1041927334</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2019</v>
       </c>
@@ -1663,7 +1659,7 @@
         <v>1053524667</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -1725,7 +1721,7 @@
         <v>1069753333</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2019</v>
       </c>
@@ -1787,7 +1783,7 @@
         <v>980959000</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2020</v>
       </c>
@@ -1849,7 +1845,7 @@
         <v>1034652667</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -1917,7 +1913,7 @@
         <v>947075000</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -1985,7 +1981,7 @@
         <v>1009566333</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -2053,7 +2049,7 @@
         <v>1003897334</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2021</v>
       </c>
@@ -2121,7 +2117,7 @@
         <v>1136444667</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2021</v>
       </c>
@@ -2189,7 +2185,7 @@
         <v>1251811667</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -2257,7 +2253,7 @@
         <v>1301976000</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2021</v>
       </c>
@@ -2325,7 +2321,7 @@
         <v>1233235667</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2022</v>
       </c>
@@ -2393,7 +2389,7 @@
         <v>1366293000</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2022</v>
       </c>
@@ -2461,7 +2457,7 @@
         <v>1420781667</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2022</v>
       </c>
@@ -2529,7 +2525,7 @@
         <v>1400780000</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2022</v>
       </c>
@@ -2597,7 +2593,7 @@
         <v>1274810999</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -2665,7 +2661,7 @@
         <v>1324885333</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2023</v>
       </c>
@@ -2733,7 +2729,7 @@
         <v>1235192001</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2023</v>
       </c>
@@ -2801,7 +2797,7 @@
         <v>1233688000</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -2869,7 +2865,7 @@
         <v>1156011000</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -2937,7 +2933,7 @@
         <v>1269569666</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -3005,7 +3001,7 @@
         <v>1250462000</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2024</v>
       </c>
@@ -3073,7 +3069,7 @@
         <v>1266318001</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -3141,7 +3137,7 @@
         <v>1171667333</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2025</v>
       </c>
@@ -3209,7 +3205,7 @@
         <v>1247385666</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2025</v>
       </c>
@@ -3277,7 +3273,7 @@
         <v>1225790667</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2025</v>
       </c>
@@ -3348,7 +3344,7 @@
         <v>1231848666</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2025</v>
       </c>
@@ -3419,7 +3415,7 @@
         <v>1158113667</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2026</v>
       </c>
@@ -3490,7 +3486,7 @@
         <v>1226073334</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2026</v>
       </c>
@@ -3561,7 +3557,7 @@
         <v>1295201667</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2026</v>
       </c>
@@ -3592,8 +3588,35 @@
       <c r="N48">
         <v>-54.350000000000009</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O48">
+        <v>168.33333333333329</v>
+      </c>
+      <c r="P48">
+        <v>29741.333333333328</v>
+      </c>
+      <c r="Q48">
+        <v>11772000</v>
+      </c>
+      <c r="R48">
+        <v>384563000</v>
+      </c>
+      <c r="S48">
+        <v>2362197667</v>
+      </c>
+      <c r="T48">
+        <v>1274253000</v>
+      </c>
+      <c r="U48">
+        <v>1087944667</v>
+      </c>
+      <c r="V48">
+        <v>647187000</v>
+      </c>
+      <c r="W48">
+        <v>440756667</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2026</v>
       </c>
@@ -3605,6 +3628,24 @@
       </c>
       <c r="H49" t="s">
         <v>25</v>
+      </c>
+      <c r="I49">
+        <v>-5.3600000000000012</v>
+      </c>
+      <c r="J49">
+        <v>-12.5</v>
+      </c>
+      <c r="K49">
+        <v>-28.57</v>
+      </c>
+      <c r="L49">
+        <v>-21.81</v>
+      </c>
+      <c r="M49">
+        <v>-2.67</v>
+      </c>
+      <c r="N49">
+        <v>-39.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/IK_Konj+Destatis_HWWI.xlsx
+++ b/data/IK_Konj+Destatis_HWWI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.mueller\Documents\FileCloud\Team Folders\IK_Server\Wirtschaft\statistische Daten\ik-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765FBFEE-BDEB-44D4-9136-9347779E1EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EA7609-8AD3-4863-9FFD-74E1EBFB7446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,6 +471,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -3588,33 +3594,6 @@
       <c r="N48">
         <v>-54.350000000000009</v>
       </c>
-      <c r="O48">
-        <v>168.33333333333329</v>
-      </c>
-      <c r="P48">
-        <v>29741.333333333328</v>
-      </c>
-      <c r="Q48">
-        <v>11772000</v>
-      </c>
-      <c r="R48">
-        <v>384563000</v>
-      </c>
-      <c r="S48">
-        <v>2362197667</v>
-      </c>
-      <c r="T48">
-        <v>1274253000</v>
-      </c>
-      <c r="U48">
-        <v>1087944667</v>
-      </c>
-      <c r="V48">
-        <v>647187000</v>
-      </c>
-      <c r="W48">
-        <v>440756667</v>
-      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49">
